--- a/Contacts_zoho.xlsx
+++ b/Contacts_zoho.xlsx
@@ -84,7 +84,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:BP258"/>
+  <dimension ref="A1:BP264"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -312,6 +312,7 @@
     <col min="223" max="223" width="19.53125" customWidth="true"/>
     <col min="224" max="224" width="19.53125" customWidth="true"/>
     <col min="225" max="225" width="19.53125" customWidth="true"/>
+    <col min="226" max="226" width="19.53125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4041,7 +4042,7 @@
         <v>45538.6612962963</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>45660.57233796296</v>
+        <v>46255.607465277775</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -38517,7 +38518,7 @@
         <v>45757.40943287037</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>45859.62273148148</v>
+        <v>46255.59946759259</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
@@ -38566,7 +38567,7 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -50685,7 +50686,7 @@
         <v>45839.470289351855</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>45839.470289351855</v>
+        <v>46245.51582175926</v>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
@@ -74345,7 +74346,7 @@
         <v>46037.60424768519</v>
       </c>
       <c r="B220" s="5" t="n">
-        <v>46037.60424768519</v>
+        <v>46247.37761574074</v>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
@@ -87517,6 +87518,2034 @@
         </is>
       </c>
       <c r="BP258" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="n">
+        <v>46234.71818287037</v>
+      </c>
+      <c r="B259" s="5" t="n">
+        <v>46234.71818287037</v>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>88 DRIVING SCHOOL LTD</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>88 DRIVING SCHOOL LTD</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Azhar</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>Cheema</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L259" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M259" s="2" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="N259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P259" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q259" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="R259" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="S259" s="2" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="T259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U259" s="2" t="inlineStr">
+        <is>
+          <t>4 Castlecombe Drive</t>
+        </is>
+      </c>
+      <c r="V259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X259" s="2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="Y259" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="Z259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA259" s="2" t="inlineStr">
+        <is>
+          <t>SW19 6RU</t>
+        </is>
+      </c>
+      <c r="AB259" s="2" t="inlineStr">
+        <is>
+          <t>+44-7931799903</t>
+        </is>
+      </c>
+      <c r="AC259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG259" s="2" t="inlineStr">
+        <is>
+          <t>4 Castlecombe Drive</t>
+        </is>
+      </c>
+      <c r="AH259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ259" s="2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="AK259" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AL259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM259" s="2" t="inlineStr">
+        <is>
+          <t>SW19 6RU</t>
+        </is>
+      </c>
+      <c r="AN259" s="2" t="inlineStr">
+        <is>
+          <t>+44-7931799903</t>
+        </is>
+      </c>
+      <c r="AO259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX259" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AY259" s="2" t="inlineStr">
+        <is>
+          <t>Your payment should reach us within 5 days from the invoice date</t>
+        </is>
+      </c>
+      <c r="AZ259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BB259" s="2" t="inlineStr">
+        <is>
+          <t>510492000001413025</t>
+        </is>
+      </c>
+      <c r="BC259" s="2" t="inlineStr">
+        <is>
+          <t>azharcheema0089@gmail.com</t>
+        </is>
+      </c>
+      <c r="BD259" s="2" t="inlineStr">
+        <is>
+          <t>+44-7931799903</t>
+        </is>
+      </c>
+      <c r="BE259" s="2" t="inlineStr">
+        <is>
+          <t>510492000001413024</t>
+        </is>
+      </c>
+      <c r="BF259" s="2" t="inlineStr">
+        <is>
+          <t>88 DRIVING SCHOOL LTD</t>
+        </is>
+      </c>
+      <c r="BG259" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="BH259" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="BI259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BJ259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM259" s="2" t="inlineStr">
+        <is>
+          <t>510492000001413024</t>
+        </is>
+      </c>
+      <c r="BN259" s="2" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="BO259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP259" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="n">
+        <v>46239.72482638889</v>
+      </c>
+      <c r="B260" s="5" t="n">
+        <v>46239.72482638889</v>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>NIFINSPIRED SKINCARE LTD</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>NIFINSPIRED SKINCARE LTD</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>Mrs.</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>Kofoworola</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>Sherifat Awosanmi</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L260" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="N260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P260" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q260" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="R260" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="S260" s="2" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="T260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U260" s="2" t="inlineStr">
+        <is>
+          <t>9 Chapman Drive</t>
+        </is>
+      </c>
+      <c r="V260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X260" s="2" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="Y260" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="Z260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA260" s="2" t="inlineStr">
+        <is>
+          <t>CV6 5HT</t>
+        </is>
+      </c>
+      <c r="AB260" s="2" t="inlineStr">
+        <is>
+          <t>+44-7789634244</t>
+        </is>
+      </c>
+      <c r="AC260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG260" s="2" t="inlineStr">
+        <is>
+          <t>9 Chapman Drive</t>
+        </is>
+      </c>
+      <c r="AH260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ260" s="2" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="AK260" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AL260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM260" s="2" t="inlineStr">
+        <is>
+          <t>CV6 5HT</t>
+        </is>
+      </c>
+      <c r="AN260" s="2" t="inlineStr">
+        <is>
+          <t>+44-7789634244</t>
+        </is>
+      </c>
+      <c r="AO260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX260" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AY260" s="2" t="inlineStr">
+        <is>
+          <t>Your payment should reach us within 5 days from the invoice date</t>
+        </is>
+      </c>
+      <c r="AZ260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BB260" s="2" t="inlineStr">
+        <is>
+          <t>510492000001429143</t>
+        </is>
+      </c>
+      <c r="BC260" s="2" t="inlineStr">
+        <is>
+          <t>rfatogun@ymail.com</t>
+        </is>
+      </c>
+      <c r="BD260" s="2" t="inlineStr">
+        <is>
+          <t>+44-7789634244</t>
+        </is>
+      </c>
+      <c r="BE260" s="2" t="inlineStr">
+        <is>
+          <t>510492000001429142</t>
+        </is>
+      </c>
+      <c r="BF260" s="2" t="inlineStr">
+        <is>
+          <t>NIFINSPIRED SKINCARE LTD</t>
+        </is>
+      </c>
+      <c r="BG260" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="BH260" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="BI260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BJ260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM260" s="2" t="inlineStr">
+        <is>
+          <t>510492000001429142</t>
+        </is>
+      </c>
+      <c r="BN260" s="2" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="BO260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP260" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="n">
+        <v>46241.67623842593</v>
+      </c>
+      <c r="B261" s="5" t="n">
+        <v>46241.67623842593</v>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>RICHMOND TOTO PROFESSIONAL CLEANING LTD</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>RICHMOND TOTO PROFESSIONAL CLEANING LTD</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>Nzolamosi</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>Nombele</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L261" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="N261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P261" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q261" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="R261" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="S261" s="2" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="T261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U261" s="2" t="inlineStr">
+        <is>
+          <t>88 Halbutt Street</t>
+        </is>
+      </c>
+      <c r="V261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X261" s="2" t="inlineStr">
+        <is>
+          <t>Dagenham</t>
+        </is>
+      </c>
+      <c r="Y261" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="Z261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA261" s="2" t="inlineStr">
+        <is>
+          <t>RM9 5AR</t>
+        </is>
+      </c>
+      <c r="AB261" s="2" t="inlineStr">
+        <is>
+          <t>+44-7391353528</t>
+        </is>
+      </c>
+      <c r="AC261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG261" s="2" t="inlineStr">
+        <is>
+          <t>88 Halbutt Street</t>
+        </is>
+      </c>
+      <c r="AH261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ261" s="2" t="inlineStr">
+        <is>
+          <t>Dagenham</t>
+        </is>
+      </c>
+      <c r="AK261" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AL261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM261" s="2" t="inlineStr">
+        <is>
+          <t>RM9 5AR</t>
+        </is>
+      </c>
+      <c r="AN261" s="2" t="inlineStr">
+        <is>
+          <t>+44-7391353528</t>
+        </is>
+      </c>
+      <c r="AO261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX261" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AY261" s="2" t="inlineStr">
+        <is>
+          <t>Your payment should reach us within 5 days from the invoice date</t>
+        </is>
+      </c>
+      <c r="AZ261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BB261" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436107</t>
+        </is>
+      </c>
+      <c r="BC261" s="2" t="inlineStr">
+        <is>
+          <t>nzolamosi@gmail.com</t>
+        </is>
+      </c>
+      <c r="BD261" s="2" t="inlineStr">
+        <is>
+          <t>+44-7391353528</t>
+        </is>
+      </c>
+      <c r="BE261" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436106</t>
+        </is>
+      </c>
+      <c r="BF261" s="2" t="inlineStr">
+        <is>
+          <t>RICHMOND TOTO PROFESSIONAL CLEANING LTD</t>
+        </is>
+      </c>
+      <c r="BG261" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="BH261" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="BI261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BJ261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM261" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436106</t>
+        </is>
+      </c>
+      <c r="BN261" s="2" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="BO261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP261" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="5" t="n">
+        <v>46244.447280092594</v>
+      </c>
+      <c r="B262" s="5" t="n">
+        <v>46244.447280092594</v>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>BORN FOR IT LTD</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>BORN FOR IT LTD</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Rasila</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>Vijay Kumar</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L262" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M262" s="2" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="N262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P262" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q262" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="R262" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="S262" s="2" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="T262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U262" s="2" t="inlineStr">
+        <is>
+          <t>3 Farber Road</t>
+        </is>
+      </c>
+      <c r="V262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X262" s="2" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="Y262" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="Z262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA262" s="2" t="inlineStr">
+        <is>
+          <t>CV2 2BE</t>
+        </is>
+      </c>
+      <c r="AB262" s="2" t="inlineStr">
+        <is>
+          <t>+44-7465695889</t>
+        </is>
+      </c>
+      <c r="AC262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG262" s="2" t="inlineStr">
+        <is>
+          <t>3 Farber Road</t>
+        </is>
+      </c>
+      <c r="AH262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ262" s="2" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="AK262" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AL262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM262" s="2" t="inlineStr">
+        <is>
+          <t>CV2 2BE</t>
+        </is>
+      </c>
+      <c r="AN262" s="2" t="inlineStr">
+        <is>
+          <t>+44-7465695889</t>
+        </is>
+      </c>
+      <c r="AO262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX262" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AY262" s="2" t="inlineStr">
+        <is>
+          <t>Your payment should reach us within 5 days from the invoice date</t>
+        </is>
+      </c>
+      <c r="AZ262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BB262" s="2" t="inlineStr">
+        <is>
+          <t>510492000001445021</t>
+        </is>
+      </c>
+      <c r="BC262" s="2" t="inlineStr">
+        <is>
+          <t>vijayaseelanv@gmail.com</t>
+        </is>
+      </c>
+      <c r="BD262" s="2" t="inlineStr">
+        <is>
+          <t>+44-7465695889</t>
+        </is>
+      </c>
+      <c r="BE262" s="2" t="inlineStr">
+        <is>
+          <t>510492000001445020</t>
+        </is>
+      </c>
+      <c r="BF262" s="2" t="inlineStr">
+        <is>
+          <t>BORN FOR IT LTD</t>
+        </is>
+      </c>
+      <c r="BG262" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="BH262" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="BI262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BJ262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM262" s="2" t="inlineStr">
+        <is>
+          <t>510492000001445020</t>
+        </is>
+      </c>
+      <c r="BN262" s="2" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="BO262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP262" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="n">
+        <v>46252.62069444444</v>
+      </c>
+      <c r="B263" s="5" t="n">
+        <v>46252.62069444444</v>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>Mr. Phone Mobile &amp; Vape</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>Mr. Phone Mobile &amp; Vape</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>Sonu</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>Sonu</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="N263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P263" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q263" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="R263" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="S263" s="2" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="T263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U263" s="2" t="inlineStr">
+        <is>
+          <t>22 Union St</t>
+        </is>
+      </c>
+      <c r="V263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X263" s="2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="Y263" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="Z263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA263" s="2" t="inlineStr">
+        <is>
+          <t>RG1 1EU</t>
+        </is>
+      </c>
+      <c r="AB263" s="2" t="inlineStr">
+        <is>
+          <t>+44-7404830098</t>
+        </is>
+      </c>
+      <c r="AC263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG263" s="2" t="inlineStr">
+        <is>
+          <t>22 Union St</t>
+        </is>
+      </c>
+      <c r="AH263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ263" s="2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="AK263" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AL263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM263" s="2" t="inlineStr">
+        <is>
+          <t>RG1 1EU</t>
+        </is>
+      </c>
+      <c r="AN263" s="2" t="inlineStr">
+        <is>
+          <t>+44-7404830098</t>
+        </is>
+      </c>
+      <c r="AO263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX263" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AY263" s="2" t="inlineStr">
+        <is>
+          <t>Your payment should reach us within 5 days from the invoice date</t>
+        </is>
+      </c>
+      <c r="AZ263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BB263" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450147</t>
+        </is>
+      </c>
+      <c r="BC263" s="2" t="inlineStr">
+        <is>
+          <t>bossuk64@gmail.com</t>
+        </is>
+      </c>
+      <c r="BD263" s="2" t="inlineStr">
+        <is>
+          <t>+44-7404830098</t>
+        </is>
+      </c>
+      <c r="BE263" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450146</t>
+        </is>
+      </c>
+      <c r="BF263" s="2" t="inlineStr">
+        <is>
+          <t>Mr. Phone Mobile &amp; Vape</t>
+        </is>
+      </c>
+      <c r="BG263" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="BH263" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="BI263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BJ263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM263" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450146</t>
+        </is>
+      </c>
+      <c r="BN263" s="2" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="BO263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP263" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="n">
+        <v>46254.583032407405</v>
+      </c>
+      <c r="B264" s="5" t="n">
+        <v>46254.58472222222</v>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>MOUNTAINS OF GLORY</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>MOUNTAINS OF GLORY</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>Neil</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>Mukherjee</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L264" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="N264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P264" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q264" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="R264" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="S264" s="2" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="T264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U264" s="2" t="inlineStr">
+        <is>
+          <t>Brunel House</t>
+        </is>
+      </c>
+      <c r="V264" s="2" t="inlineStr">
+        <is>
+          <t>Fitzalan Road</t>
+        </is>
+      </c>
+      <c r="W264" s="2" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="X264" s="2" t="inlineStr">
+        <is>
+          <t>Wales</t>
+        </is>
+      </c>
+      <c r="Y264" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="Z264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA264" s="2" t="inlineStr">
+        <is>
+          <t>CF24 0EB</t>
+        </is>
+      </c>
+      <c r="AB264" s="2" t="inlineStr">
+        <is>
+          <t>+44-07943507507</t>
+        </is>
+      </c>
+      <c r="AC264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG264" s="2" t="inlineStr">
+        <is>
+          <t>Brunel House</t>
+        </is>
+      </c>
+      <c r="AH264" s="2" t="inlineStr">
+        <is>
+          <t>Fitzalan Road</t>
+        </is>
+      </c>
+      <c r="AI264" s="2" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="AJ264" s="2" t="inlineStr">
+        <is>
+          <t>Wales</t>
+        </is>
+      </c>
+      <c r="AK264" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AL264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM264" s="2" t="inlineStr">
+        <is>
+          <t>CF24 0EB</t>
+        </is>
+      </c>
+      <c r="AN264" s="2" t="inlineStr">
+        <is>
+          <t>+44-07943507507</t>
+        </is>
+      </c>
+      <c r="AO264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX264" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AY264" s="2" t="inlineStr">
+        <is>
+          <t>Your payment should reach us within 5 days from the invoice date</t>
+        </is>
+      </c>
+      <c r="AZ264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BB264" s="2" t="inlineStr">
+        <is>
+          <t>510492000001460107</t>
+        </is>
+      </c>
+      <c r="BC264" s="2" t="inlineStr">
+        <is>
+          <t>neil.mountainsofglory@gmail.com</t>
+        </is>
+      </c>
+      <c r="BD264" s="2" t="inlineStr">
+        <is>
+          <t>+44-07943507507</t>
+        </is>
+      </c>
+      <c r="BE264" s="2" t="inlineStr">
+        <is>
+          <t>510492000001460106</t>
+        </is>
+      </c>
+      <c r="BF264" s="2" t="inlineStr">
+        <is>
+          <t>MOUNTAINS OF GLORY</t>
+        </is>
+      </c>
+      <c r="BG264" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="BH264" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="BI264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BJ264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM264" s="2" t="inlineStr">
+        <is>
+          <t>510492000001460106</t>
+        </is>
+      </c>
+      <c r="BN264" s="2" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="BO264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP264" s="2" t="inlineStr">
         <is>
           <t/>
         </is>
